--- a/Mainstream Framework Integration/scipy_agent/output/sales_analysis.xlsx
+++ b/Mainstream Framework Integration/scipy_agent/output/sales_analysis.xlsx
@@ -1,44 +1,45 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zxyxi\PycharmProjects\PythonProject3\temp3\excel_agent\samples\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2"/>
+    <workbookView xWindow="240" yWindow="120" windowWidth="14940" windowHeight="9225" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId3"/>
-    <sheet name="Summary" sheetId="2" r:id="rId4"/>
-    <sheet name="Evaluation Warning" sheetId="3" r:id="rId5"/>
+    <sheet name="Evaluation Warning" sheetId="2" r:id="rId4"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
-  <si>
-    <t>Sales</t>
-  </si>
-  <si>
-    <t>Year</t>
-  </si>
-  <si>
-    <t>Column 0: 0 anomalies
-Column 1: 1 anomalies
-Column 0: trend calculated (14 points)
-Column 1: trend calculated (14 points)</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+  <si>
+    <t>row_count</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>column_count</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>numeric_columns</t>
+  </si>
+  <si>
+    <t>['Year', 'Sales']</t>
+  </si>
+  <si>
+    <t>analysis_results</t>
+  </si>
+  <si>
+    <t>{'trend': {'Year': [1.8857142857142861, 2.2571428571428576, 2.914285714285713, 3.9999999999999982, 4.999999999999998, 5.999999999999997, 6.999999999999997, 7.9999999999999964, 8.999999999999995, 9.999999999999996, 10.999999999999996, 11.999999999999995, 12.999999999999993, 13.999999999999995, 14.999999999999993, 15.999999999999988], 'Sales': [-317.71428571428976, 1782.8571428571422, 2487.7142857142844, 1799.1428571428564, -299.42857142857156, -29445747.714285716, 117783539.42857139, 166859979.42857137, 117783557.99999996, -29445739.14285715, -308.0000000000001, 1780.571428571428, 2487.7142857142844, 1799.1428571428564, 956.5714285714257, -593.1428571428596]}, 'anomaly': {'Year': [], 'Sales': [{'index': 7, 'value': np.float64(343535130.0), 'zscore': 3.8729833454830835}]}}</t>
   </si>
   <si>
     <t>Evaluation Only. Created with Aspose.Cells for Python via .NET. Copyright 2003 - 2026 Aspose Pty Ltd.</t>
@@ -47,36 +48,13 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -87,18 +65,12 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -115,29 +87,15 @@
       <alignment/>
       <protection/>
     </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment/>
       <protection/>
     </xf>
@@ -150,7 +108,6 @@
     <cellStyle name="Comma" xfId="4" builtinId="3"/>
     <cellStyle name="Comma [0]" xfId="5" builtinId="6"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -247,7 +204,7 @@
         <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
         <a:srgbClr val="ED7D31"/>
@@ -259,7 +216,7 @@
         <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
         <a:srgbClr val="70AD47"/>
@@ -306,6 +263,23 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
@@ -341,6 +315,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -492,162 +483,40 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B17"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
-  <cols>
-    <col min="2" max="2" width="10.5" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F29C4B82-1A0D-4AC6-AE03-4A141384BAA4}">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
-    <row r="1" spans="1:2" ht="13.8">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:2" ht="12.75">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
     </row>
-    <row r="2" spans="1:2" ht="13.8">
-      <c r="A2" s="2">
+    <row r="2" spans="1:2" ht="12.75">
+      <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="2">
-        <v>100</v>
+      <c r="B2" t="s">
+        <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="13.8">
-      <c r="A3" s="2">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2">
-        <v>110</v>
+    <row r="3" spans="1:2" ht="12.75">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="13.8">
-      <c r="A4" s="2">
-        <v>3</v>
-      </c>
-      <c r="B4" s="2">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="13.8">
-      <c r="A5" s="2">
-        <v>4</v>
-      </c>
-      <c r="B5" s="2">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="13.8">
-      <c r="A6" s="2">
-        <v>5</v>
-      </c>
-      <c r="B6" s="2">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="13.8">
-      <c r="A7" s="2">
+    <row r="4" spans="1:2" ht="12.75">
+      <c r="A4" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="13.8">
-      <c r="A8" s="2">
+      <c r="B4" t="s">
         <v>7</v>
-      </c>
-      <c r="B8" s="2">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="13.8">
-      <c r="A9" s="2">
-        <v>8</v>
-      </c>
-      <c r="B9" s="4">
-        <v>343535130</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="13.8">
-      <c r="A10" s="2">
-        <v>9</v>
-      </c>
-      <c r="B10" s="2">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="13.8">
-      <c r="A11" s="2">
-        <v>10</v>
-      </c>
-      <c r="B11" s="2">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="13.8">
-      <c r="A12" s="2">
-        <v>11</v>
-      </c>
-      <c r="B12" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="13.8">
-      <c r="A13" s="2">
-        <v>12</v>
-      </c>
-      <c r="B13" s="2">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" ht="13.8">
-      <c r="A14" s="2">
-        <v>13</v>
-      </c>
-      <c r="B14" s="2">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" ht="13.8">
-      <c r="A15" s="2">
-        <v>14</v>
-      </c>
-      <c r="B15" s="2">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" ht="13.8">
-      <c r="A16" s="2">
-        <v>15</v>
-      </c>
-      <c r="B16" s="2">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="13.8">
-      <c r="A17" s="2">
-        <v>16</v>
-      </c>
-      <c r="B17" s="2">
-        <v>100</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BE6AEE4-F37D-4428-865A-D6DB18D0BAA4}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
-  <sheetData>
-    <row r="1" spans="1:1" ht="14.25">
-      <c r="A1" t="s">
-        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -655,14 +524,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AB03F66-8F93-4A9E-8ED0-8ED4BEA1BAA4}">
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53515F2A-3B77-427F-BF37-3835352DBAA4}">
   <dimension ref="A5"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
     <row r="5" spans="1:1" ht="23.25" customHeight="1">
-      <c r="A5" s="5" t="s">
-        <v>3</v>
+      <c r="A5" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
